--- a/data/trans_dic/P56$privada-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P56$privada-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,23</t>
+          <t>0,0; 33,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,3</t>
+          <t>0,0; 21,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,47 +732,47 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,12; 19,37</t>
+          <t>2,18; 18,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,05; 32,2</t>
+          <t>4,0; 31,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,38; 20,76</t>
+          <t>2,33; 21,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,28</t>
+          <t>0,0; 12,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,85; 17,31</t>
+          <t>5,31; 17,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,99; 25,23</t>
+          <t>2,65; 23,11</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,06; 16,12</t>
+          <t>3,04; 16,25</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,17</t>
+          <t>0,0; 8,28</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,49; 14,87</t>
+          <t>5,1; 14,36</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,26; 19,29</t>
+          <t>2,26; 17,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,7; 21,35</t>
+          <t>5,12; 22,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,54; 31,21</t>
+          <t>9,94; 30,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,73; 26,46</t>
+          <t>11,81; 26,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,61; 20,8</t>
+          <t>4,77; 21,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,55; 23,44</t>
+          <t>9,92; 22,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,65; 27,96</t>
+          <t>12,33; 29,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,67; 24,62</t>
+          <t>16,57; 24,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,36; 16,77</t>
+          <t>4,82; 16,59</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,86; 19,54</t>
+          <t>10,08; 20,01</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13,97; 25,93</t>
+          <t>13,73; 27,37</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,4; 23,13</t>
+          <t>15,93; 23,32</t>
         </is>
       </c>
     </row>
@@ -944,47 +944,47 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>14,82%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>11,54%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>14,53%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>15,47%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>18,12%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>10,05%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>13,13%</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
           <t>14,89%</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>11,54%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>14,53%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>15,47%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>18,29%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>10,05%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>13,13%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>14,89%</t>
-        </is>
-      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,19%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 16,5</t>
+          <t>1,84; 16,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,93; 18,15</t>
+          <t>4,05; 18,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,05; 22,74</t>
+          <t>7,12; 22,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,34; 21,71</t>
+          <t>10,05; 21,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,63; 19,59</t>
+          <t>5,61; 20,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,85; 19,74</t>
+          <t>9,59; 20,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,59; 22,71</t>
+          <t>9,47; 23,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,01; 22,43</t>
+          <t>14,93; 21,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,11; 16,57</t>
+          <t>5,55; 16,22</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,01; 17,61</t>
+          <t>9,24; 17,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,64; 20,96</t>
+          <t>10,5; 20,87</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,44; 20,36</t>
+          <t>14,4; 20,51</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2359</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5521</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7749</t>
+          <t>8235</t>
         </is>
       </c>
     </row>
@@ -1363,12 +1363,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3632</t>
+          <t>0; 4358</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5851</t>
+          <t>0; 4658</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1378,47 +1378,47 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>628; 5742</t>
+          <t>675; 5810</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>894; 7107</t>
+          <t>882; 6938</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1002; 8746</t>
+          <t>983; 9063</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4233</t>
+          <t>0; 5220</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3099; 9175</t>
+          <t>3160; 10282</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1044; 8815</t>
+          <t>927; 8073</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1942; 10247</t>
+          <t>1932; 10328</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 5086</t>
+          <t>0; 5154</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4538; 12288</t>
+          <t>4609; 12987</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12970</t>
+          <t>13736</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>40391</t>
+          <t>44033</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>53361</t>
+          <t>57769</t>
         </is>
       </c>
     </row>
@@ -1571,62 +1571,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>801; 6832</t>
+          <t>801; 6292</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2110; 12185</t>
+          <t>2920; 12837</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5376; 15916</t>
+          <t>5068; 15758</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8491; 19161</t>
+          <t>9167; 20509</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3297; 14866</t>
+          <t>3413; 15320</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17208; 38228</t>
+          <t>16179; 37344</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16515; 36517</t>
+          <t>16102; 37973</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33009; 48764</t>
+          <t>35782; 53861</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5727; 17921</t>
+          <t>5155; 17730</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21715; 43018</t>
+          <t>22204; 44060</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25372; 47097</t>
+          <t>24933; 49714</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>44358; 62560</t>
+          <t>46761; 68470</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15198</t>
+          <t>16095</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>45911</t>
+          <t>49909</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>61110</t>
+          <t>66003</t>
         </is>
       </c>
     </row>
@@ -1779,62 +1779,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>854; 7968</t>
+          <t>887; 7995</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3089; 14249</t>
+          <t>3182; 14551</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5085; 16395</t>
+          <t>5130; 16313</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10552; 22156</t>
+          <t>10915; 22962</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5267; 18327</t>
+          <t>5244; 19030</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20218; 40510</t>
+          <t>19684; 41665</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16480; 39014</t>
+          <t>16272; 40246</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>37689; 56308</t>
+          <t>41110; 59639</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8667; 23499</t>
+          <t>7866; 23003</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25556; 49965</t>
+          <t>26208; 49401</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25946; 51109</t>
+          <t>25617; 50892</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>50999; 71897</t>
+          <t>55311; 78774</t>
         </is>
       </c>
     </row>
